--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.14274306322613</v>
+        <v>11.07319574777425</v>
       </c>
       <c r="D2" t="n">
-        <v>67.00117379573162</v>
+        <v>10.88769074180639</v>
       </c>
       <c r="E2" t="n">
-        <v>21.38818707062752</v>
+        <v>3.475580398976972</v>
       </c>
       <c r="F2" t="n">
-        <v>21.09068321251418</v>
+        <v>3.427236022033554</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.26179277978369</v>
+        <v>10.76754132671485</v>
       </c>
       <c r="D3" t="n">
-        <v>64.18206613445632</v>
+        <v>10.42958574684915</v>
       </c>
       <c r="E3" t="n">
-        <v>21.38818707062752</v>
+        <v>3.475580398976972</v>
       </c>
       <c r="F3" t="n">
-        <v>21.09068321251418</v>
+        <v>3.427236022033554</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>80.19237764642428</v>
+        <v>13.03126136754395</v>
       </c>
       <c r="D4" t="n">
-        <v>81.1686418713394</v>
+        <v>13.18990430409265</v>
       </c>
       <c r="E4" t="n">
-        <v>21.38818707062752</v>
+        <v>3.475580398976972</v>
       </c>
       <c r="F4" t="n">
-        <v>21.09068321251418</v>
+        <v>3.427236022033554</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.15505980828014</v>
+        <v>8.962697218845523</v>
       </c>
       <c r="D5" t="n">
-        <v>55.38379369153719</v>
+        <v>8.999866474874793</v>
       </c>
       <c r="E5" t="n">
-        <v>21.38818707062752</v>
+        <v>3.475580398976972</v>
       </c>
       <c r="F5" t="n">
-        <v>21.09068321251418</v>
+        <v>3.427236022033554</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>64.04212370060374</v>
+        <v>10.40684510134811</v>
       </c>
       <c r="D6" t="n">
-        <v>64.99983283741084</v>
+        <v>10.56247283607926</v>
       </c>
       <c r="E6" t="n">
-        <v>21.38818707062752</v>
+        <v>3.475580398976972</v>
       </c>
       <c r="F6" t="n">
-        <v>21.09068321251418</v>
+        <v>3.427236022033554</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.3273487649445</v>
+        <v>8.178194174303481</v>
       </c>
       <c r="D7" t="n">
-        <v>51.30731261079882</v>
+        <v>8.337438299254808</v>
       </c>
       <c r="E7" t="n">
-        <v>21.38818707062752</v>
+        <v>3.475580398976972</v>
       </c>
       <c r="F7" t="n">
-        <v>21.09068321251418</v>
+        <v>3.427236022033554</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.60653800936838</v>
+        <v>3.998562426522362</v>
       </c>
       <c r="D8" t="n">
-        <v>25.55835921387707</v>
+        <v>4.153233372255024</v>
       </c>
       <c r="E8" t="n">
-        <v>21.38818707062752</v>
+        <v>3.475580398976972</v>
       </c>
       <c r="F8" t="n">
-        <v>21.09068321251418</v>
+        <v>3.427236022033554</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.30602355608268</v>
+        <v>2.162228827863435</v>
       </c>
       <c r="D9" t="n">
-        <v>13.77688766520007</v>
+        <v>2.238744245595012</v>
       </c>
       <c r="E9" t="n">
-        <v>21.38818707062752</v>
+        <v>3.475580398976972</v>
       </c>
       <c r="F9" t="n">
-        <v>21.09068321251418</v>
+        <v>3.427236022033554</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
